--- a/tests/test_data/date_name_tag.xlsx
+++ b/tests/test_data/date_name_tag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\aurora-robot-tools\tests\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0CC959-41AD-4C81-8022-D27CD4494FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DDC754-798A-41E3-963E-9A815141E3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="12645" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="2775" windowWidth="21600" windowHeight="12645" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input Table" sheetId="1" r:id="rId1"/>
@@ -3421,22 +3421,22 @@
         <v>71</v>
       </c>
       <c r="C3" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" s="40">
-        <v>10</v>
+        <v>15.1</v>
       </c>
       <c r="E3" s="39">
         <v>0.98</v>
       </c>
       <c r="F3" s="10">
-        <v>650</v>
+        <v>340</v>
       </c>
       <c r="G3" s="40">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H3" s="10">
-        <v>650</v>
+        <v>340</v>
       </c>
       <c r="I3" s="27" t="s">
         <v>73</v>
@@ -3445,10 +3445,10 @@
         <v>75</v>
       </c>
       <c r="K3" s="10">
-        <v>11</v>
+        <v>13.8</v>
       </c>
       <c r="L3" s="40">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="M3" s="39">
         <v>0.96</v>
@@ -3457,7 +3457,7 @@
         <v>160</v>
       </c>
       <c r="O3" s="40">
-        <v>0.88</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P3" s="41">
         <v>160</v>
